--- a/doc/BotruyvanGEO-Paris/09-nhachu.xlsx
+++ b/doc/BotruyvanGEO-Paris/09-nhachu.xlsx
@@ -1749,6 +1749,11 @@
           <t>ĐIỂM ƯU TIÊN = Giá trị DT (Cao 3 · TB 2 · Thấp 1) × Nhiệt độ (Hot 3 · Warm 2 · Existing 2 · Cold 1) × Ưu tiên (P1 3 · P2 2 · P3 1) × CƠ HỘI GEO. ⚠ Paris chưa có mốc traffic AI → CƠ HỘI GEO = 1 cho mọi cụm; chấm lại sau tháng Setup.</t>
         </is>
       </c>
+      <c r="S3" s="20" t="inlineStr">
+        <is>
+          <t>Hai cột điểm có nguồn khác nhau và LỆCH NHAU LÀ BÌNH THƯỜNG: «ĐIỂM CỤM» cộng bottom-up từ 17 truy vấn của cụm; «% ĐIỂM (chỉ mục)» lấy từ knowledge/geo-bo-truy-van-index.md — đây là con số Agent dùng để lập kế hoạch. Sau tháng Setup có mốc traffic thật thì chấm lại CƠ HỘI GEO và hợp nhất hai nguồn.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
